--- a/backend/data/financials_by_company/0815.HK.xlsx
+++ b/backend/data/financials_by_company/0815.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,610 +677,667 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-80250</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>68310000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-321000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-321000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>54575000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>19802000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4202621000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>67989000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>48187000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-24734000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>26639000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1905000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>54815750</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9966000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4265931000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>1954081000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1954081000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="W2" t="n">
-        <v>9966000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>9966000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9966000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>32168000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-22202000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-44609000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22407000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-859000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>21548000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1044000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-321000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>321000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-24734000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>26639000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1905000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>47783000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>63310000</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>12026000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2408511000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>2301000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>789000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>63011000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>18636000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>44375000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>111093000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4202621000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4313714000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4313714000</v>
-      </c>
+        <v>-9004000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-354575.4858</v>
+        <v>-1547750</v>
       </c>
       <c r="C3" t="n">
-        <v>0.153297</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>59680000</v>
+        <v>-22032000</v>
       </c>
       <c r="E3" t="n">
-        <v>-2313000</v>
+        <v>-6191000</v>
       </c>
       <c r="F3" t="n">
-        <v>-2313000</v>
+        <v>-6191000</v>
       </c>
       <c r="G3" t="n">
-        <v>39614000</v>
+        <v>-61522000</v>
       </c>
       <c r="H3" t="n">
-        <v>26255000</v>
+        <v>34254000</v>
       </c>
       <c r="I3" t="n">
-        <v>5346381000</v>
+        <v>3165768000</v>
       </c>
       <c r="J3" t="n">
-        <v>57367000</v>
+        <v>-28223000</v>
       </c>
       <c r="K3" t="n">
-        <v>31112000</v>
+        <v>-62477000</v>
       </c>
       <c r="L3" t="n">
-        <v>-19344000</v>
+        <v>-19998000</v>
       </c>
       <c r="M3" t="n">
-        <v>25091000</v>
+        <v>22581000</v>
       </c>
       <c r="N3" t="n">
-        <v>5747000</v>
+        <v>2583000</v>
       </c>
       <c r="O3" t="n">
-        <v>41572424.5142</v>
+        <v>-56878750</v>
       </c>
       <c r="P3" t="n">
-        <v>14549000</v>
+        <v>-120766000</v>
       </c>
       <c r="Q3" t="n">
-        <v>5420819000</v>
+        <v>3288810000</v>
       </c>
       <c r="R3" t="n">
-        <v>127000</v>
+        <v>1578000</v>
       </c>
       <c r="S3" t="n">
-        <v>1954081000</v>
+        <v>1868422000</v>
       </c>
       <c r="T3" t="n">
-        <v>1954081000</v>
+        <v>1868422000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007</v>
+        <v>-0.065</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007</v>
+        <v>-0.065</v>
       </c>
       <c r="W3" t="n">
-        <v>14549000</v>
+        <v>-120766000</v>
       </c>
       <c r="X3" t="n">
-        <v>14549000</v>
+        <v>-120766000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>14549000</v>
+        <v>-120766000</v>
       </c>
       <c r="AA3" t="n">
-        <v>34516000</v>
+        <v>24070000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-19967000</v>
+        <v>-144836000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-25065000</v>
+        <v>-59244000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5098000</v>
+        <v>-85592000</v>
       </c>
       <c r="AE3" t="n">
-        <v>923000</v>
+        <v>534000</v>
       </c>
       <c r="AF3" t="n">
-        <v>6021000</v>
+        <v>-85058000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1130000</v>
+        <v>1667000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2313000</v>
+        <v>-6191000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1637000</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>6203000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
       <c r="AK3" t="n">
-        <v>3950000</v>
+        <v>6191000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-19344000</v>
+        <v>-19998000</v>
       </c>
       <c r="AM3" t="n">
-        <v>25091000</v>
+        <v>22581000</v>
       </c>
       <c r="AN3" t="n">
-        <v>5747000</v>
+        <v>2583000</v>
       </c>
       <c r="AO3" t="n">
-        <v>34187000</v>
+        <v>-57235000</v>
       </c>
       <c r="AP3" t="n">
-        <v>74438000</v>
+        <v>123042000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2727000</v>
+        <v>1651000</v>
       </c>
       <c r="AR3" t="n">
-        <v>771000</v>
+        <v>1015000</v>
       </c>
       <c r="AS3" t="n">
-        <v>74487000</v>
+        <v>120995000</v>
       </c>
       <c r="AT3" t="n">
-        <v>23560000</v>
+        <v>41950000</v>
       </c>
       <c r="AU3" t="n">
-        <v>50927000</v>
+        <v>79045000</v>
       </c>
       <c r="AV3" t="n">
-        <v>108625000</v>
+        <v>65807000</v>
       </c>
       <c r="AW3" t="n">
-        <v>5346381000</v>
+        <v>3165768000</v>
       </c>
       <c r="AX3" t="n">
-        <v>5455006000</v>
+        <v>3231575000</v>
       </c>
       <c r="AY3" t="n">
-        <v>5455006000</v>
+        <v>3231575000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1547750</v>
+        <v>-354575.4858</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.153297</v>
       </c>
       <c r="D4" t="n">
-        <v>-22032000</v>
+        <v>59680000</v>
       </c>
       <c r="E4" t="n">
-        <v>-6191000</v>
+        <v>-2313000</v>
       </c>
       <c r="F4" t="n">
-        <v>-6191000</v>
+        <v>-2313000</v>
       </c>
       <c r="G4" t="n">
-        <v>-61522000</v>
+        <v>39614000</v>
       </c>
       <c r="H4" t="n">
-        <v>34254000</v>
+        <v>26255000</v>
       </c>
       <c r="I4" t="n">
-        <v>3165768000</v>
+        <v>5346381000</v>
       </c>
       <c r="J4" t="n">
-        <v>-28223000</v>
+        <v>57367000</v>
       </c>
       <c r="K4" t="n">
-        <v>-62477000</v>
+        <v>31112000</v>
       </c>
       <c r="L4" t="n">
-        <v>-19998000</v>
+        <v>-19344000</v>
       </c>
       <c r="M4" t="n">
-        <v>22581000</v>
+        <v>25091000</v>
       </c>
       <c r="N4" t="n">
-        <v>2583000</v>
+        <v>5747000</v>
       </c>
       <c r="O4" t="n">
-        <v>-56878750</v>
+        <v>41572424.5142</v>
       </c>
       <c r="P4" t="n">
-        <v>-120766000</v>
+        <v>14549000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3288810000</v>
+        <v>5420819000</v>
       </c>
       <c r="R4" t="n">
-        <v>1578000</v>
+        <v>127000</v>
       </c>
       <c r="S4" t="n">
-        <v>1868422000</v>
+        <v>1954081000</v>
       </c>
       <c r="T4" t="n">
-        <v>1868422000</v>
+        <v>1954081000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.065</v>
+        <v>0.007</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.065</v>
+        <v>0.007</v>
       </c>
       <c r="W4" t="n">
-        <v>-120766000</v>
+        <v>14549000</v>
       </c>
       <c r="X4" t="n">
-        <v>-120766000</v>
+        <v>14549000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-120766000</v>
+        <v>14549000</v>
       </c>
       <c r="AA4" t="n">
-        <v>24070000</v>
+        <v>34516000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-144836000</v>
+        <v>-19967000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-59244000</v>
+        <v>-25065000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-85592000</v>
+        <v>5098000</v>
       </c>
       <c r="AE4" t="n">
-        <v>534000</v>
+        <v>923000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-85058000</v>
+        <v>6021000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1667000</v>
+        <v>1130000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-6191000</v>
+        <v>-2313000</v>
       </c>
       <c r="AI4" t="n">
-        <v>6203000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+        <v>-1637000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>6191000</v>
+        <v>3950000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-19998000</v>
+        <v>-19344000</v>
       </c>
       <c r="AM4" t="n">
-        <v>22581000</v>
+        <v>25091000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2583000</v>
+        <v>5747000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-57235000</v>
+        <v>34187000</v>
       </c>
       <c r="AP4" t="n">
-        <v>123042000</v>
+        <v>74438000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1651000</v>
+        <v>2727000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1015000</v>
+        <v>771000</v>
       </c>
       <c r="AS4" t="n">
-        <v>120995000</v>
+        <v>74487000</v>
       </c>
       <c r="AT4" t="n">
-        <v>41950000</v>
+        <v>23560000</v>
       </c>
       <c r="AU4" t="n">
-        <v>79045000</v>
+        <v>50927000</v>
       </c>
       <c r="AV4" t="n">
-        <v>65807000</v>
+        <v>108625000</v>
       </c>
       <c r="AW4" t="n">
-        <v>3165768000</v>
+        <v>5346381000</v>
       </c>
       <c r="AX4" t="n">
-        <v>3231575000</v>
+        <v>5455006000</v>
       </c>
       <c r="AY4" t="n">
-        <v>3231575000</v>
+        <v>5455006000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6017.750913</v>
+        <v>-80250</v>
       </c>
       <c r="C5" t="n">
-        <v>2e-06</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>57266000</v>
+        <v>57983000</v>
       </c>
       <c r="E5" t="n">
-        <v>-2420537000</v>
+        <v>-321000</v>
       </c>
       <c r="F5" t="n">
-        <v>-2420537000</v>
+        <v>-321000</v>
       </c>
       <c r="G5" t="n">
-        <v>-2412925000</v>
+        <v>50898000</v>
       </c>
       <c r="H5" t="n">
-        <v>35945000</v>
+        <v>19802000</v>
       </c>
       <c r="I5" t="n">
-        <v>2164578000</v>
+        <v>4093459000</v>
       </c>
       <c r="J5" t="n">
-        <v>-2363271000</v>
+        <v>57662000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2399216000</v>
+        <v>37860000</v>
       </c>
       <c r="L5" t="n">
-        <v>-12759000</v>
+        <v>-20034000</v>
       </c>
       <c r="M5" t="n">
-        <v>14181000</v>
+        <v>21232000</v>
       </c>
       <c r="N5" t="n">
-        <v>1422000</v>
+        <v>1198000</v>
       </c>
       <c r="O5" t="n">
-        <v>7605982.249087</v>
+        <v>51138750</v>
       </c>
       <c r="P5" t="n">
-        <v>-2412925000</v>
+        <v>9966000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2287631000</v>
+        <v>4118008000</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>1628401000</v>
+        <v>1954081000</v>
       </c>
       <c r="T5" t="n">
-        <v>1628401000</v>
+        <v>1954081000</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.482</v>
+        <v>0.005</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.482</v>
+        <v>0.005</v>
       </c>
       <c r="W5" t="n">
-        <v>-2412925000</v>
+        <v>9966000</v>
       </c>
       <c r="X5" t="n">
-        <v>-2412925000</v>
+        <v>9966000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2412925000</v>
+        <v>9966000</v>
       </c>
       <c r="AA5" t="n">
-        <v>466000</v>
+        <v>32168000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2413391000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>-22202000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-40932000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>-2413391000</v>
+        <v>18730000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6000</v>
+        <v>-2102000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2413397000</v>
+        <v>16628000</v>
       </c>
       <c r="AG5" t="n">
-        <v>3151000</v>
+        <v>982000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2420537000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>12026000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2408511000</v>
-      </c>
+        <v>-321000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>321000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-12759000</v>
+        <v>-20034000</v>
       </c>
       <c r="AM5" t="n">
-        <v>14181000</v>
+        <v>21232000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1422000</v>
+        <v>1198000</v>
       </c>
       <c r="AO5" t="n">
-        <v>15892000</v>
+        <v>38136000</v>
       </c>
       <c r="AP5" t="n">
-        <v>123053000</v>
+        <v>24549000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-9004000</v>
+        <v>2301000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1488000</v>
+        <v>789000</v>
       </c>
       <c r="AS5" t="n">
-        <v>132296000</v>
+        <v>24514000</v>
       </c>
       <c r="AT5" t="n">
-        <v>30400000</v>
+        <v>3154000</v>
       </c>
       <c r="AU5" t="n">
-        <v>101896000</v>
+        <v>21360000</v>
       </c>
       <c r="AV5" t="n">
-        <v>138945000</v>
+        <v>62685000</v>
       </c>
       <c r="AW5" t="n">
-        <v>2164578000</v>
+        <v>4093459000</v>
       </c>
       <c r="AX5" t="n">
-        <v>2303523000</v>
+        <v>4156144000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2303523000</v>
+        <v>4156144000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.025489</v>
+      </c>
+      <c r="D6" t="n">
+        <v>40365000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-22018000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15381000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2991131000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40365000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>24984000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-11813000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12037000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>224000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-22018000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>586329000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3041703000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>2390437000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2390437000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="W6" t="n">
+        <v>586329000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>586329000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>586329000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-34635000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>620964000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>608347000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12617000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>330000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12947000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1092000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-11813000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>12037000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>224000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>21597000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>50572000</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>724000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>54332000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2322000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>52010000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>72169000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2991131000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3063300000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3063300000</v>
       </c>
     </row>
   </sheetData>
@@ -1294,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,209 +1703,95 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1954080706</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1954080706</v>
-      </c>
-      <c r="D2" t="n">
-        <v>402029000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>460110000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>862358000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1090426000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>460110000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1108000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>461437000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>461437000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1218348000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>756911000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>461437000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>67871000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1219435000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1255434000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>15935000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>15935000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>760528000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1778000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1369000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>409000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>409000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>758750000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>401620000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>699000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>400921000</v>
-      </c>
+        <v>9803000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>7413000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>245694000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>119010000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>27475000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>99209000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1978876000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>129700000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>4932000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1327000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1327000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>123441000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-161476000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>284917000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>76256000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>185258000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>17934000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5469000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1849176000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>29890000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>39800000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>51967000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1111866000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>643449000</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="n">
-        <v>468417000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>26864000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>7308000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>55139000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-18462000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>73601000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>526342000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>526342000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>526342000</v>
-      </c>
+        <v>20848000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>996000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>7377000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>7377000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>165567000</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1954080706</v>
@@ -1857,43 +1800,43 @@
         <v>1954080706</v>
       </c>
       <c r="D3" t="n">
-        <v>427391000</v>
+        <v>411821000</v>
       </c>
       <c r="E3" t="n">
-        <v>430085000</v>
+        <v>389941000</v>
       </c>
       <c r="F3" t="n">
-        <v>872671000</v>
+        <v>843120000</v>
       </c>
       <c r="G3" t="n">
-        <v>1084300000</v>
+        <v>1060372000</v>
       </c>
       <c r="H3" t="n">
-        <v>430085000</v>
+        <v>389941000</v>
       </c>
       <c r="I3" t="n">
-        <v>6191000</v>
+        <v>5439000</v>
       </c>
       <c r="J3" t="n">
-        <v>451471000</v>
+        <v>436738000</v>
       </c>
       <c r="K3" t="n">
-        <v>451471000</v>
+        <v>436738000</v>
       </c>
       <c r="L3" t="n">
-        <v>1238100000</v>
+        <v>1257883000</v>
       </c>
       <c r="M3" t="n">
-        <v>786629000</v>
+        <v>821145000</v>
       </c>
       <c r="N3" t="n">
-        <v>451471000</v>
+        <v>436738000</v>
       </c>
       <c r="O3" t="n">
-        <v>89330000</v>
+        <v>90366000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1250529000</v>
+        <v>-1264683000</v>
       </c>
       <c r="Q3" t="n">
         <v>1255434000</v>
@@ -1905,156 +1848,158 @@
         <v>15935000</v>
       </c>
       <c r="T3" t="n">
-        <v>784949000</v>
+        <v>885286000</v>
       </c>
       <c r="U3" t="n">
-        <v>5640000</v>
+        <v>14989000</v>
       </c>
       <c r="V3" t="n">
-        <v>2083000</v>
+        <v>11722000</v>
       </c>
       <c r="W3" t="n">
-        <v>1355000</v>
+        <v>1549000</v>
       </c>
       <c r="X3" t="n">
-        <v>2202000</v>
+        <v>1718000</v>
       </c>
       <c r="Y3" t="n">
-        <v>2202000</v>
+        <v>1718000</v>
       </c>
       <c r="Z3" t="n">
-        <v>779309000</v>
+        <v>870297000</v>
       </c>
       <c r="AA3" t="n">
-        <v>425189000</v>
+        <v>410103000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3989000</v>
+        <v>3721000</v>
       </c>
       <c r="AC3" t="n">
-        <v>421200000</v>
+        <v>406382000</v>
       </c>
       <c r="AD3" t="n">
         <v>7413000</v>
       </c>
       <c r="AE3" t="n">
-        <v>342409000</v>
+        <v>415496000</v>
       </c>
       <c r="AF3" t="n">
-        <v>128284000</v>
+        <v>154166000</v>
       </c>
       <c r="AG3" t="n">
-        <v>24294000</v>
+        <v>21618000</v>
       </c>
       <c r="AH3" t="n">
-        <v>189831000</v>
+        <v>239712000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2023049000</v>
+        <v>2143169000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>159440000</v>
+        <v>212500000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>762000</v>
       </c>
       <c r="AL3" t="n">
-        <v>4709000</v>
+        <v>6295000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>7348000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7348000</v>
+      </c>
       <c r="AO3" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21386000</v>
+        <v>46797000</v>
       </c>
       <c r="AR3" t="n">
-        <v>8910000</v>
+        <v>34321000</v>
       </c>
       <c r="AS3" t="n">
         <v>12476000</v>
       </c>
       <c r="AT3" t="n">
-        <v>133333000</v>
+        <v>151298000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-147475000</v>
+        <v>-144258000</v>
       </c>
       <c r="AV3" t="n">
-        <v>280808000</v>
+        <v>295556000</v>
       </c>
       <c r="AW3" t="n">
-        <v>331000</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>3277000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>148577000</v>
+      </c>
       <c r="AY3" t="n">
-        <v>76042000</v>
+        <v>82119000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>188845000</v>
+        <v>194135000</v>
       </c>
       <c r="BA3" t="n">
-        <v>15590000</v>
+        <v>16025000</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1863609000</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
+        <v>1930669000</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>107900000</v>
+        <v>172191000</v>
       </c>
       <c r="BF3" t="n">
-        <v>5563000</v>
+        <v>3227000</v>
       </c>
       <c r="BG3" t="n">
-        <v>1087498000</v>
+        <v>1056274000</v>
       </c>
       <c r="BH3" t="n">
-        <v>564432000</v>
+        <v>516537000</v>
       </c>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>523066000</v>
+        <v>539737000</v>
       </c>
       <c r="BK3" t="n">
-        <v>64810000</v>
+        <v>67034000</v>
       </c>
       <c r="BL3" t="n">
-        <v>16095000</v>
+        <v>21862000</v>
       </c>
       <c r="BM3" t="n">
-        <v>57061000</v>
+        <v>20856000</v>
       </c>
       <c r="BN3" t="n">
-        <v>-22293000</v>
+        <v>-14343000</v>
       </c>
       <c r="BO3" t="n">
-        <v>79354000</v>
+        <v>35199000</v>
       </c>
       <c r="BP3" t="n">
-        <v>524682000</v>
+        <v>589225000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>524682000</v>
+        <v>589225000</v>
       </c>
       <c r="BR3" t="n">
-        <v>524682000</v>
+        <v>589225000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1954080706</v>
@@ -2063,43 +2008,43 @@
         <v>1954080706</v>
       </c>
       <c r="D4" t="n">
-        <v>411821000</v>
+        <v>427391000</v>
       </c>
       <c r="E4" t="n">
-        <v>389941000</v>
+        <v>430085000</v>
       </c>
       <c r="F4" t="n">
-        <v>843120000</v>
+        <v>872671000</v>
       </c>
       <c r="G4" t="n">
-        <v>1060372000</v>
+        <v>1084300000</v>
       </c>
       <c r="H4" t="n">
-        <v>389941000</v>
+        <v>430085000</v>
       </c>
       <c r="I4" t="n">
-        <v>5439000</v>
+        <v>6191000</v>
       </c>
       <c r="J4" t="n">
-        <v>436738000</v>
+        <v>451471000</v>
       </c>
       <c r="K4" t="n">
-        <v>436738000</v>
+        <v>451471000</v>
       </c>
       <c r="L4" t="n">
-        <v>1257883000</v>
+        <v>1238100000</v>
       </c>
       <c r="M4" t="n">
-        <v>821145000</v>
+        <v>786629000</v>
       </c>
       <c r="N4" t="n">
-        <v>436738000</v>
+        <v>451471000</v>
       </c>
       <c r="O4" t="n">
-        <v>90366000</v>
+        <v>89330000</v>
       </c>
       <c r="P4" t="n">
-        <v>-1264683000</v>
+        <v>-1250529000</v>
       </c>
       <c r="Q4" t="n">
         <v>1255434000</v>
@@ -2111,357 +2056,551 @@
         <v>15935000</v>
       </c>
       <c r="T4" t="n">
-        <v>885286000</v>
+        <v>784949000</v>
       </c>
       <c r="U4" t="n">
-        <v>14989000</v>
+        <v>5640000</v>
       </c>
       <c r="V4" t="n">
-        <v>11722000</v>
+        <v>2083000</v>
       </c>
       <c r="W4" t="n">
-        <v>1549000</v>
+        <v>1355000</v>
       </c>
       <c r="X4" t="n">
-        <v>1718000</v>
+        <v>2202000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1718000</v>
+        <v>2202000</v>
       </c>
       <c r="Z4" t="n">
-        <v>870297000</v>
+        <v>779309000</v>
       </c>
       <c r="AA4" t="n">
-        <v>410103000</v>
+        <v>425189000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3721000</v>
+        <v>3989000</v>
       </c>
       <c r="AC4" t="n">
-        <v>406382000</v>
+        <v>421200000</v>
       </c>
       <c r="AD4" t="n">
         <v>7413000</v>
       </c>
       <c r="AE4" t="n">
-        <v>415496000</v>
+        <v>342409000</v>
       </c>
       <c r="AF4" t="n">
-        <v>154166000</v>
+        <v>128284000</v>
       </c>
       <c r="AG4" t="n">
-        <v>21618000</v>
+        <v>24294000</v>
       </c>
       <c r="AH4" t="n">
-        <v>239712000</v>
+        <v>189831000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2143169000</v>
+        <v>2023049000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>212500000</v>
+        <v>159440000</v>
       </c>
       <c r="AK4" t="n">
-        <v>762000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>6295000</v>
+        <v>4709000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7348000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>7348000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>46797000</v>
+        <v>21386000</v>
       </c>
       <c r="AR4" t="n">
-        <v>34321000</v>
+        <v>8910000</v>
       </c>
       <c r="AS4" t="n">
         <v>12476000</v>
       </c>
       <c r="AT4" t="n">
-        <v>151298000</v>
+        <v>133333000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-144258000</v>
+        <v>-147475000</v>
       </c>
       <c r="AV4" t="n">
-        <v>295556000</v>
+        <v>280808000</v>
       </c>
       <c r="AW4" t="n">
-        <v>3277000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>148577000</v>
-      </c>
+        <v>331000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>82119000</v>
+        <v>76042000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>194135000</v>
+        <v>188845000</v>
       </c>
       <c r="BA4" t="n">
-        <v>16025000</v>
+        <v>15590000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1930669000</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
+        <v>1863609000</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
       <c r="BE4" t="n">
-        <v>172191000</v>
+        <v>107900000</v>
       </c>
       <c r="BF4" t="n">
-        <v>3227000</v>
+        <v>5563000</v>
       </c>
       <c r="BG4" t="n">
-        <v>1056274000</v>
+        <v>1087498000</v>
       </c>
       <c r="BH4" t="n">
-        <v>516537000</v>
+        <v>564432000</v>
       </c>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>539737000</v>
+        <v>523066000</v>
       </c>
       <c r="BK4" t="n">
-        <v>67034000</v>
+        <v>64810000</v>
       </c>
       <c r="BL4" t="n">
-        <v>21862000</v>
+        <v>16095000</v>
       </c>
       <c r="BM4" t="n">
-        <v>20856000</v>
+        <v>57061000</v>
       </c>
       <c r="BN4" t="n">
-        <v>-14343000</v>
+        <v>-22293000</v>
       </c>
       <c r="BO4" t="n">
-        <v>35199000</v>
+        <v>79354000</v>
       </c>
       <c r="BP4" t="n">
-        <v>589225000</v>
+        <v>524682000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>589225000</v>
+        <v>524682000</v>
       </c>
       <c r="BR4" t="n">
-        <v>589225000</v>
+        <v>524682000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1628400589</v>
+        <v>1954080706</v>
       </c>
       <c r="C5" t="n">
-        <v>1628400589</v>
+        <v>1954080706</v>
       </c>
       <c r="D5" t="n">
-        <v>238343000</v>
+        <v>402029000</v>
       </c>
       <c r="E5" t="n">
-        <v>303878000</v>
+        <v>460110000</v>
       </c>
       <c r="F5" t="n">
-        <v>631086000</v>
+        <v>862358000</v>
       </c>
       <c r="G5" t="n">
-        <v>980322000</v>
+        <v>1090426000</v>
       </c>
       <c r="H5" t="n">
-        <v>303878000</v>
+        <v>460110000</v>
       </c>
       <c r="I5" t="n">
-        <v>8343000</v>
+        <v>1108000</v>
       </c>
       <c r="J5" t="n">
-        <v>401086000</v>
+        <v>461437000</v>
       </c>
       <c r="K5" t="n">
-        <v>401086000</v>
+        <v>461437000</v>
       </c>
       <c r="L5" t="n">
-        <v>1233307000</v>
+        <v>1218348000</v>
       </c>
       <c r="M5" t="n">
-        <v>832221000</v>
+        <v>756911000</v>
       </c>
       <c r="N5" t="n">
-        <v>401086000</v>
+        <v>461437000</v>
       </c>
       <c r="O5" t="n">
-        <v>90366000</v>
+        <v>67871000</v>
       </c>
       <c r="P5" t="n">
-        <v>-1143917000</v>
+        <v>-1219435000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1101638000</v>
+        <v>1255434000</v>
       </c>
       <c r="R5" t="n">
-        <v>13284000</v>
+        <v>15935000</v>
       </c>
       <c r="S5" t="n">
-        <v>13284000</v>
+        <v>15935000</v>
       </c>
       <c r="T5" t="n">
-        <v>628170000</v>
+        <v>760528000</v>
       </c>
       <c r="U5" t="n">
-        <v>28083000</v>
+        <v>1778000</v>
       </c>
       <c r="V5" t="n">
-        <v>13902000</v>
+        <v>1369000</v>
       </c>
       <c r="W5" t="n">
-        <v>9803000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>4378000</v>
+        <v>409000</v>
       </c>
       <c r="Y5" t="n">
-        <v>4378000</v>
+        <v>409000</v>
       </c>
       <c r="Z5" t="n">
-        <v>600087000</v>
+        <v>758750000</v>
       </c>
       <c r="AA5" t="n">
-        <v>233965000</v>
+        <v>401620000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3965000</v>
+        <v>699000</v>
       </c>
       <c r="AC5" t="n">
-        <v>230000000</v>
+        <v>400921000</v>
       </c>
       <c r="AD5" t="n">
-        <v>20848000</v>
+        <v>7413000</v>
       </c>
       <c r="AE5" t="n">
-        <v>223146000</v>
+        <v>245694000</v>
       </c>
       <c r="AF5" t="n">
-        <v>91315000</v>
+        <v>119010000</v>
       </c>
       <c r="AG5" t="n">
-        <v>19600000</v>
+        <v>27475000</v>
       </c>
       <c r="AH5" t="n">
-        <v>112231000</v>
+        <v>99209000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1861477000</v>
+        <v>1978876000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>281068000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>996000</v>
-      </c>
+        <v>129700000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>8626000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>7377000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>7377000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+        <v>4932000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>97208000</v>
+        <v>1327000</v>
       </c>
       <c r="AR5" t="n">
-        <v>97208000</v>
+        <v>1327000</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>166861000</v>
+        <v>123441000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-146104000</v>
+        <v>-161476000</v>
       </c>
       <c r="AV5" t="n">
-        <v>312965000</v>
+        <v>284917000</v>
       </c>
       <c r="AW5" t="n">
-        <v>4257000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>165567000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>106002000</v>
+        <v>76256000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>186314000</v>
+        <v>185258000</v>
       </c>
       <c r="BA5" t="n">
-        <v>16392000</v>
+        <v>17934000</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>5469000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1580409000</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
+        <v>1849176000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>29890000</v>
+      </c>
       <c r="BE5" t="n">
-        <v>140415000</v>
+        <v>39800000</v>
       </c>
       <c r="BF5" t="n">
-        <v>20989000</v>
+        <v>51967000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1054154000</v>
+        <v>1111866000</v>
       </c>
       <c r="BH5" t="n">
-        <v>529287000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
+        <v>643449000</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>524867000</v>
-      </c>
-      <c r="BK5" t="inlineStr"/>
+        <v>468417000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>26864000</v>
+      </c>
       <c r="BL5" t="n">
-        <v>24540000</v>
+        <v>7308000</v>
       </c>
       <c r="BM5" t="n">
-        <v>23506000</v>
+        <v>55139000</v>
       </c>
       <c r="BN5" t="n">
-        <v>-12018000</v>
+        <v>-18462000</v>
       </c>
       <c r="BO5" t="n">
-        <v>35524000</v>
+        <v>73601000</v>
       </c>
       <c r="BP5" t="n">
-        <v>316805000</v>
+        <v>526342000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>316805000</v>
+        <v>526342000</v>
       </c>
       <c r="BR5" t="n">
-        <v>316805000</v>
+        <v>526342000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2981337559</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2981337559</v>
+      </c>
+      <c r="D6" t="n">
+        <v>110561000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1331820000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1442839000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>128712000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1331820000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>561000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1332839000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1332839000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1331940000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-899000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1332839000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-85167000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-441428000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1616244000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>25373000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25373000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>530853000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>709000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>655000</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>54000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>54000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>530144000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>110507000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>507000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>418923000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>132470000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>731000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>285722000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1862793000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1203937000</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>342000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>1105751000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1105751000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1019000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1019000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>96825000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-150163000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>246988000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>67901000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>164366000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>14721000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>658856000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>239500000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>156000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>184768000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>184763000</v>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1844000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>273000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>232315000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>232315000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>232315000</v>
       </c>
     </row>
   </sheetData>
@@ -2475,7 +2614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2704,444 +2843,386 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Stock Based Compensation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-70699000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-377663000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>365384000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>-6243000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>526342000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-474000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>524682000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2134000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5315000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>46871000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-27263000</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>-12279000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-12279000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-377663000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>365384000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>61275000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>68100000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1905000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-2487000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>-2487000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-4997000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-4997000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-1246000</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>25275000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-1246000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-64456000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-126482000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1993000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-59860000</v>
-      </c>
+        <v>3066000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-33000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-24924000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-43658000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>24495000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>19802000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1136000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18666000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-23255000</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>11994000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-126584000</v>
+        <v>76790000</v>
       </c>
       <c r="C3" t="n">
-        <v>-266682000</v>
+        <v>-280001000</v>
       </c>
       <c r="D3" t="n">
-        <v>281500000</v>
+        <v>452588000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>156447000</v>
       </c>
       <c r="F3" t="n">
-        <v>-4261000</v>
+        <v>-10581000</v>
       </c>
       <c r="G3" t="n">
-        <v>524682000</v>
+        <v>589225000</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>589225000</v>
+        <v>316805000</v>
       </c>
       <c r="J3" t="n">
-        <v>-64543000</v>
+        <v>272420000</v>
       </c>
       <c r="K3" t="n">
-        <v>-8279000</v>
+        <v>317574000</v>
       </c>
       <c r="L3" t="n">
-        <v>6839000</v>
+        <v>15467000</v>
       </c>
       <c r="M3" t="n">
-        <v>-25761000</v>
+        <v>-22696000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>156447000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>156447000</v>
       </c>
       <c r="P3" t="n">
-        <v>14818000</v>
+        <v>172587000</v>
       </c>
       <c r="Q3" t="n">
-        <v>14818000</v>
+        <v>172587000</v>
       </c>
       <c r="R3" t="n">
-        <v>-266682000</v>
+        <v>-280001000</v>
       </c>
       <c r="S3" t="n">
-        <v>281500000</v>
+        <v>452588000</v>
       </c>
       <c r="T3" t="n">
-        <v>66059000</v>
+        <v>-132525000</v>
       </c>
       <c r="U3" t="n">
-        <v>64397000</v>
+        <v>-126900000</v>
       </c>
       <c r="V3" t="n">
-        <v>5747000</v>
+        <v>2787000</v>
       </c>
       <c r="W3" t="n">
-        <v>-40000</v>
+        <v>1398000</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1398000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-40000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4045000</v>
+        <v>-9810000</v>
       </c>
       <c r="AD3" t="n">
-        <v>216000</v>
+        <v>771000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-4261000</v>
+        <v>-10581000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-122323000</v>
+        <v>87371000</v>
       </c>
       <c r="AG3" t="n">
-        <v>631000</v>
+        <v>-1811000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-164567000</v>
+        <v>124774000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-43463000</v>
+        <v>92605000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-43406000</v>
+        <v>-31260000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-157000</v>
+        <v>234000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-31224000</v>
+        <v>-1955000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-46317000</v>
+        <v>65150000</v>
       </c>
       <c r="AN3" t="n">
-        <v>17976000</v>
+        <v>17612000</v>
       </c>
       <c r="AO3" t="n">
-        <v>26255000</v>
+        <v>34254000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3938000</v>
+        <v>12179000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22317000</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>22075000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6203000</v>
+      </c>
       <c r="AS3" t="n">
-        <v>-1636000</v>
+        <v>-19000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-18807000</v>
-      </c>
+        <v>-152971000</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>76790000</v>
+        <v>-126584000</v>
       </c>
       <c r="C4" t="n">
-        <v>-280001000</v>
+        <v>-266682000</v>
       </c>
       <c r="D4" t="n">
-        <v>452588000</v>
+        <v>281500000</v>
       </c>
       <c r="E4" t="n">
-        <v>156447000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-10581000</v>
+        <v>-4261000</v>
       </c>
       <c r="G4" t="n">
-        <v>589225000</v>
+        <v>524682000</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>316805000</v>
+        <v>589225000</v>
       </c>
       <c r="J4" t="n">
-        <v>272420000</v>
+        <v>-64543000</v>
       </c>
       <c r="K4" t="n">
-        <v>317574000</v>
+        <v>-8279000</v>
       </c>
       <c r="L4" t="n">
-        <v>15467000</v>
+        <v>6839000</v>
       </c>
       <c r="M4" t="n">
-        <v>-22696000</v>
+        <v>-25761000</v>
       </c>
       <c r="N4" t="n">
-        <v>156447000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>156447000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>172587000</v>
+        <v>14818000</v>
       </c>
       <c r="Q4" t="n">
-        <v>172587000</v>
+        <v>14818000</v>
       </c>
       <c r="R4" t="n">
-        <v>-280001000</v>
+        <v>-266682000</v>
       </c>
       <c r="S4" t="n">
-        <v>452588000</v>
+        <v>281500000</v>
       </c>
       <c r="T4" t="n">
-        <v>-132525000</v>
+        <v>66059000</v>
       </c>
       <c r="U4" t="n">
-        <v>-126900000</v>
+        <v>64397000</v>
       </c>
       <c r="V4" t="n">
-        <v>2787000</v>
+        <v>5747000</v>
       </c>
       <c r="W4" t="n">
-        <v>1398000</v>
+        <v>-40000</v>
       </c>
       <c r="X4" t="n">
-        <v>1398000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-40000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-9810000</v>
+        <v>-4045000</v>
       </c>
       <c r="AD4" t="n">
-        <v>771000</v>
+        <v>216000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-10581000</v>
+        <v>-4261000</v>
       </c>
       <c r="AF4" t="n">
-        <v>87371000</v>
+        <v>-122323000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1811000</v>
+        <v>631000</v>
       </c>
       <c r="AH4" t="n">
-        <v>124774000</v>
+        <v>-164567000</v>
       </c>
       <c r="AI4" t="n">
-        <v>92605000</v>
+        <v>-43463000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-31260000</v>
+        <v>-43406000</v>
       </c>
       <c r="AK4" t="n">
-        <v>234000</v>
+        <v>-157000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1955000</v>
+        <v>-31224000</v>
       </c>
       <c r="AM4" t="n">
-        <v>65150000</v>
+        <v>-46317000</v>
       </c>
       <c r="AN4" t="n">
-        <v>17612000</v>
+        <v>17976000</v>
       </c>
       <c r="AO4" t="n">
-        <v>34254000</v>
+        <v>26255000</v>
       </c>
       <c r="AP4" t="n">
-        <v>12179000</v>
+        <v>3938000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22075000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>6203000</v>
-      </c>
+        <v>22317000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>-19000</v>
+        <v>-1636000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-152971000</v>
-      </c>
+        <v>-18807000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-908491000</v>
+        <v>-70699000</v>
       </c>
       <c r="C5" t="n">
-        <v>-215000000</v>
+        <v>-377663000</v>
       </c>
       <c r="D5" t="n">
-        <v>230000000</v>
+        <v>365384000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-39247000</v>
+        <v>-6243000</v>
       </c>
       <c r="G5" t="n">
-        <v>316805000</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>526342000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-474000</v>
+      </c>
       <c r="I5" t="n">
-        <v>1192989000</v>
+        <v>524682000</v>
       </c>
       <c r="J5" t="n">
-        <v>-876184000</v>
+        <v>2134000</v>
       </c>
       <c r="K5" t="n">
-        <v>-4464000</v>
+        <v>5315000</v>
       </c>
       <c r="L5" t="n">
-        <v>-95000</v>
+        <v>46871000</v>
       </c>
       <c r="M5" t="n">
-        <v>-14172000</v>
+        <v>-27263000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -3150,95 +3231,225 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>15000000</v>
+        <v>-12279000</v>
       </c>
       <c r="Q5" t="n">
-        <v>15000000</v>
+        <v>-12279000</v>
       </c>
       <c r="R5" t="n">
-        <v>-215000000</v>
+        <v>-377663000</v>
       </c>
       <c r="S5" t="n">
-        <v>230000000</v>
+        <v>365384000</v>
       </c>
       <c r="T5" t="n">
-        <v>-2476000</v>
+        <v>61275000</v>
       </c>
       <c r="U5" t="n">
-        <v>7008000</v>
+        <v>68100000</v>
       </c>
       <c r="V5" t="n">
-        <v>1422000</v>
+        <v>1905000</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+        <v>-2487000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>-2487000</v>
+      </c>
       <c r="Z5" t="n">
-        <v>-5606000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>25275000</v>
-      </c>
+        <v>-4997000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-30881000</v>
+        <v>-4997000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5300000</v>
+        <v>-1246000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3066000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-8366000</v>
+        <v>-1246000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-869244000</v>
+        <v>-64456000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-19125000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-894776000</v>
+        <v>-126482000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-56637000</v>
+        <v>1993000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-176229000</v>
+        <v>-59860000</v>
       </c>
       <c r="AK5" t="n">
-        <v>100000</v>
+        <v>-33000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-885082000</v>
+        <v>-24924000</v>
       </c>
       <c r="AM5" t="n">
-        <v>223072000</v>
+        <v>-43691000</v>
       </c>
       <c r="AN5" t="n">
-        <v>10608000</v>
+        <v>24495000</v>
       </c>
       <c r="AO5" t="n">
-        <v>35945000</v>
+        <v>19802000</v>
       </c>
       <c r="AP5" t="n">
-        <v>10630000</v>
+        <v>1136000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25315000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11994000</v>
-      </c>
+        <v>18666000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-2413397000</v>
+        <v>-23255000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>403591000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-310690000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>226630000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>205549000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-57819000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>232315000</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>526816000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-294501000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>142538000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>38577000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-16571000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>205549000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>205549000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-84060000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-84060000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-310690000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>226630000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-898449000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-199700000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>595000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-641525000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>-641525000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-50028000</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-50028000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-7791000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-7791000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>461410000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-19098000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>251457000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1645000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>292687000</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>-46811000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>7226000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15262000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>15381000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>362000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>15019000</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-548683000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>659675000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>84850000</v>
       </c>
     </row>
   </sheetData>
@@ -3768,177 +3979,177 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EH1" t="inlineStr">
@@ -4013,7 +4224,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Wantian  Chen', 'age': 51, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 449359, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guosheng  Song', 'age': 62, 'title': 'VP &amp; Executive Vice Chairman', 'yearBorn': 1963, 'fiscalYear': 2025, 'totalPay': 1152351, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hon To  Chan FCCA', 'age': 49, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Wantian  Chen', 'age': 51, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 449404, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guosheng  Song', 'age': 62, 'title': 'VP &amp; Executive Vice Chairman', 'yearBorn': 1963, 'fiscalYear': 2025, 'totalPay': 1152468, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hon To  Chan FCCA', 'age': 49, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4031,28 +4242,28 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="T2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.325</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.32</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.33</v>
-      </c>
       <c r="X2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.325</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.335</v>
       </c>
       <c r="AA2" t="n">
         <v>1496275200</v>
@@ -4061,31 +4272,31 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="AD2" t="n">
-        <v>33.000004</v>
+        <v>30.500002</v>
       </c>
       <c r="AE2" t="n">
-        <v>13878000</v>
+        <v>11796000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13878000</v>
+        <v>11796000</v>
       </c>
       <c r="AG2" t="n">
-        <v>17421502</v>
+        <v>14699412</v>
       </c>
       <c r="AH2" t="n">
-        <v>18944334</v>
+        <v>12590600</v>
       </c>
       <c r="AI2" t="n">
-        <v>18944334</v>
+        <v>12590600</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.335</v>
+        <v>0.305</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -4094,13 +4305,13 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1023441472</v>
+        <v>945907968</v>
       </c>
       <c r="AO2" t="n">
-        <v>1023441394</v>
+        <v>945907955</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.31</v>
+        <v>0.295</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.93</v>
@@ -4112,13 +4323,13 @@
         <v>0.092</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.33409768</v>
+        <v>0.30878723</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4379</v>
+        <v>0.3982</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.584475</v>
+        <v>0.575125</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4135,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>861188416</v>
+        <v>846281728</v>
       </c>
       <c r="BB2" t="n">
         <v>0.19139999</v>
@@ -4156,10 +4367,10 @@
         <v>3101337559</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.5176894</v>
+        <v>0.5177417</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.6374479</v>
+        <v>0.5890969</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -4177,16 +4388,16 @@
         <v>0.01</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.281</v>
+        <v>0.276</v>
       </c>
       <c r="BP2" t="n">
-        <v>27.775</v>
+        <v>27.294</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.015384674</v>
+        <v>-0.26506025</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BS2" t="n">
         <v>0.03</v>
@@ -4200,7 +4411,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.33</v>
+        <v>0.305</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4297,139 +4508,139 @@
         </is>
       </c>
       <c r="CW2" t="n">
-        <v>0</v>
+        <v>-4.6874957</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.33</v>
+        <v>0.305</v>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
           <t>CHI SILVER GP</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>China Silver Group Limited</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DC2" t="n">
+        <v>1781769576</v>
+      </c>
+      <c r="DD2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>finmb_225229546</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DF2" t="n">
+      <c r="DH2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
         <v>1356658200000</v>
       </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>0.32 - 0.335</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="n">
+        <v>-0.014999986</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>0.3 - 0.325</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DN2" t="n">
-        <v>17421502</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.02000001</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.064516164</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0.31 - 0.93</t>
-        </is>
+      <c r="DQ2" t="n">
+        <v>14699412</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.6</v>
+        <v>0.01000002</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.64516133</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1.5384674</v>
+        <v>0.033898376</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>0.295 - 0.93</t>
+        </is>
       </c>
       <c r="DU2" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.6720429999999999</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-26.506025</v>
+      </c>
+      <c r="DX2" t="n">
         <v>1743113777</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="DY2" t="n">
         <v>1743113777</v>
       </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
         <v>0.01</v>
       </c>
-      <c r="DY2" t="n">
-        <v>-0.10789999</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.24640328</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.25447497</v>
-      </c>
       <c r="EB2" t="n">
-        <v>-0.43539068</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="EC2" t="n">
+        <v>-0.23405324</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.27012497</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.46968046</v>
+      </c>
+      <c r="EF2" t="n">
         <v>15</v>
       </c>
-      <c r="ED2" t="n">
+      <c r="EG2" t="n">
         <v>15</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>China Silver Group Limited</t>
-        </is>
       </c>
       <c r="EH2" t="inlineStr"/>
     </row>
